--- a/PSMBench_evaluation_results/transitions_match_results_whole.xlsx
+++ b/PSMBench_evaluation_results/transitions_match_results_whole.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="33">
   <si>
     <t>Protocol</t>
   </si>
@@ -62,25 +62,31 @@
     <t>IMAP</t>
   </si>
   <si>
-    <t>deepseek-reasoner</t>
+    <t>DS-R1</t>
   </si>
   <si>
-    <t>gpt-4o-mini</t>
+    <t>Gpt4o-Mini</t>
   </si>
   <si>
-    <t>claude-3-7-sonnet-20250219</t>
+    <t>Claude3</t>
   </si>
   <si>
-    <t>gemini-2.0-flash</t>
+    <t>Gemini2</t>
   </si>
   <si>
-    <t>deepseek-chat</t>
+    <t>DS-V3</t>
   </si>
   <si>
-    <t>qwq</t>
+    <t>QWQ</t>
   </si>
   <si>
-    <t>mistral-small3.1</t>
+    <t>QWen3</t>
+  </si>
+  <si>
+    <t>Gemma3</t>
+  </si>
+  <si>
+    <t>Mistral</t>
   </si>
   <si>
     <t>POP3</t>
@@ -1272,11 +1278,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
-    <col min="2" max="2" width="29.375" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="5" width="8.375" customWidth="1"/>
     <col min="6" max="6" width="12.625" customWidth="1"/>
@@ -1518,103 +1524,103 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D8">
         <v>11</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I8">
-        <v>0.455</v>
+        <v>0.182</v>
       </c>
       <c r="J8">
-        <v>0.323</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9">
+        <v>17</v>
+      </c>
+      <c r="D9">
         <v>11</v>
       </c>
-      <c r="C9">
-        <v>21</v>
-      </c>
-      <c r="D9">
-        <v>18</v>
-      </c>
       <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
         <v>8</v>
       </c>
-      <c r="F9">
-        <v>10</v>
-      </c>
       <c r="G9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9">
-        <v>0.381</v>
+        <v>0.176</v>
       </c>
       <c r="I9">
-        <v>0.444</v>
+        <v>0.273</v>
       </c>
       <c r="J9">
-        <v>0.41</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C10">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D10">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H10">
-        <v>0.303</v>
+        <v>0.25</v>
       </c>
       <c r="I10">
-        <v>0.556</v>
+        <v>0.455</v>
       </c>
       <c r="J10">
-        <v>0.392</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>18</v>
@@ -1626,123 +1632,123 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H11">
-        <v>0.308</v>
+        <v>0.381</v>
       </c>
       <c r="I11">
         <v>0.444</v>
       </c>
       <c r="J11">
-        <v>0.364</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D12">
         <v>18</v>
       </c>
       <c r="E12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G12">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H12">
-        <v>0.231</v>
+        <v>0.303</v>
       </c>
       <c r="I12">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="J12">
-        <v>0.316</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>18</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H13">
-        <v>0.45</v>
+        <v>0.308</v>
       </c>
       <c r="I13">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="J13">
-        <v>0.474</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="D14">
         <v>18</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H14">
-        <v>0.2</v>
+        <v>0.231</v>
       </c>
       <c r="I14">
-        <v>0.056</v>
+        <v>0.5</v>
       </c>
       <c r="J14">
-        <v>0.087</v>
+        <v>0.316</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C15">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D15">
         <v>18</v>
@@ -1754,155 +1760,155 @@
         <v>9</v>
       </c>
       <c r="G15">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H15">
-        <v>0.31</v>
+        <v>0.45</v>
       </c>
       <c r="I15">
         <v>0.5</v>
       </c>
       <c r="J15">
-        <v>0.383</v>
+        <v>0.474</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C16">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G16">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>0.062</v>
+        <v>0.2</v>
       </c>
       <c r="I16">
-        <v>0.059</v>
+        <v>0.056</v>
       </c>
       <c r="J16">
-        <v>0.061</v>
+        <v>0.087</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C17">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G17">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>0.054</v>
+        <v>0.5</v>
       </c>
       <c r="I17">
-        <v>0.118</v>
+        <v>0.222</v>
       </c>
       <c r="J17">
-        <v>0.074</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C18">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G18">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H18">
-        <v>0.044</v>
+        <v>0.158</v>
       </c>
       <c r="I18">
-        <v>0.118</v>
+        <v>0.333</v>
       </c>
       <c r="J18">
-        <v>0.065</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" t="s">
-        <v>14</v>
-      </c>
       <c r="C19">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G19">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H19">
-        <v>0.042</v>
+        <v>0.31</v>
       </c>
       <c r="I19">
-        <v>0.118</v>
+        <v>0.5</v>
       </c>
       <c r="J19">
-        <v>0.062</v>
+        <v>0.383</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D20">
         <v>17</v>
@@ -1914,59 +1920,59 @@
         <v>16</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H20">
-        <v>0.167</v>
+        <v>0.062</v>
       </c>
       <c r="I20">
         <v>0.059</v>
       </c>
       <c r="J20">
-        <v>0.087</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C21">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D21">
         <v>17</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H21">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
       <c r="I21">
-        <v>0.059</v>
+        <v>0.118</v>
       </c>
       <c r="J21">
-        <v>0.057</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C22">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D22">
         <v>17</v>
@@ -1978,464 +1984,464 @@
         <v>15</v>
       </c>
       <c r="G22">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H22">
-        <v>0.054</v>
+        <v>0.044</v>
       </c>
       <c r="I22">
         <v>0.118</v>
       </c>
       <c r="J22">
-        <v>0.074</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C23">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="D23">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G23">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="H23">
-        <v>0.09</v>
+        <v>0.042</v>
       </c>
       <c r="I23">
-        <v>0.37</v>
+        <v>0.118</v>
       </c>
       <c r="J23">
-        <v>0.145</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C24">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G24">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>0.121</v>
+        <v>0.167</v>
       </c>
       <c r="I24">
-        <v>0.148</v>
+        <v>0.059</v>
       </c>
       <c r="J24">
-        <v>0.133</v>
+        <v>0.087</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C25">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="D25">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G25">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="H25">
-        <v>0.065</v>
+        <v>0.056</v>
       </c>
       <c r="I25">
-        <v>0.333</v>
+        <v>0.059</v>
       </c>
       <c r="J25">
-        <v>0.109</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C26">
-        <v>126</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E26">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G26">
-        <v>107</v>
+        <v>5</v>
       </c>
       <c r="H26">
-        <v>0.151</v>
+        <v>0.167</v>
       </c>
       <c r="I26">
-        <v>0.704</v>
+        <v>0.059</v>
       </c>
       <c r="J26">
-        <v>0.248</v>
+        <v>0.087</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C27">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D27">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G27">
         <v>18</v>
       </c>
       <c r="H27">
-        <v>0.143</v>
+        <v>0.053</v>
       </c>
       <c r="I27">
-        <v>0.111</v>
+        <v>0.059</v>
       </c>
       <c r="J27">
-        <v>0.125</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="D28">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C29">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="D29">
         <v>27</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F29">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G29">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D30">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="H30">
-        <v>0.667</v>
+        <v>0.121</v>
       </c>
       <c r="I30">
-        <v>0.632</v>
+        <v>0.148</v>
       </c>
       <c r="J30">
-        <v>0.649</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="D31">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G31">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="H31">
-        <v>0.069</v>
+        <v>0.065</v>
       </c>
       <c r="I31">
-        <v>0.105</v>
+        <v>0.333</v>
       </c>
       <c r="J31">
-        <v>0.083</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C32">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="D32">
+        <v>27</v>
+      </c>
+      <c r="E32">
         <v>19</v>
       </c>
-      <c r="E32">
-        <v>3</v>
-      </c>
       <c r="F32">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G32">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="H32">
-        <v>0.054</v>
+        <v>0.151</v>
       </c>
       <c r="I32">
-        <v>0.158</v>
+        <v>0.704</v>
       </c>
       <c r="J32">
-        <v>0.08</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33">
         <v>21</v>
       </c>
-      <c r="B33" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33">
-        <v>23</v>
-      </c>
       <c r="D33">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G33">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E34">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G34">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H34">
-        <v>0.353</v>
+        <v>0</v>
       </c>
       <c r="I34">
-        <v>0.632</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>0.453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35">
         <v>21</v>
       </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35">
-        <v>2</v>
-      </c>
       <c r="D35">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C36">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D36">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G36">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H36">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>0.065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2443,214 +2449,214 @@
         <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C37">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D37">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E37">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F37">
+        <v>27</v>
+      </c>
+      <c r="G37">
         <v>12</v>
       </c>
-      <c r="G37">
-        <v>6</v>
-      </c>
       <c r="H37">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>0.538</v>
+        <v>0</v>
       </c>
       <c r="J37">
-        <v>0.609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38">
+        <v>18</v>
+      </c>
+      <c r="D38">
+        <v>19</v>
+      </c>
+      <c r="E38">
         <v>12</v>
       </c>
-      <c r="C38">
-        <v>25</v>
-      </c>
-      <c r="D38">
-        <v>26</v>
-      </c>
-      <c r="E38">
-        <v>8</v>
-      </c>
       <c r="F38">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G38">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H38">
-        <v>0.32</v>
+        <v>0.667</v>
       </c>
       <c r="I38">
-        <v>0.308</v>
+        <v>0.632</v>
       </c>
       <c r="J38">
-        <v>0.314</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C39">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="D39">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E39">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G39">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="H39">
-        <v>0.333</v>
+        <v>0.069</v>
       </c>
       <c r="I39">
-        <v>0.769</v>
+        <v>0.105</v>
       </c>
       <c r="J39">
-        <v>0.465</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C40">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="D40">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E40">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G40">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H40">
-        <v>0.248</v>
+        <v>0.054</v>
       </c>
       <c r="I40">
-        <v>0.962</v>
+        <v>0.158</v>
       </c>
       <c r="J40">
-        <v>0.394</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C41">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D41">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E41">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G41">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H41">
-        <v>0.438</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>0.538</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>0.483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42">
+        <v>34</v>
+      </c>
+      <c r="D42">
+        <v>19</v>
+      </c>
+      <c r="E42">
+        <v>12</v>
+      </c>
+      <c r="F42">
+        <v>7</v>
+      </c>
+      <c r="G42">
         <v>22</v>
       </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42">
-        <v>7</v>
-      </c>
-      <c r="D42">
-        <v>26</v>
-      </c>
-      <c r="E42">
-        <v>2</v>
-      </c>
-      <c r="F42">
-        <v>24</v>
-      </c>
-      <c r="G42">
-        <v>5</v>
-      </c>
       <c r="H42">
-        <v>0.286</v>
+        <v>0.353</v>
       </c>
       <c r="I42">
-        <v>0.077</v>
+        <v>0.632</v>
       </c>
       <c r="J42">
-        <v>0.121</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C43">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D43">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G43">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -2667,31 +2673,31 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C44">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="D44">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E44">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G44">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="H44">
-        <v>0.207</v>
+        <v>0.5</v>
       </c>
       <c r="I44">
-        <v>0.6</v>
+        <v>0.158</v>
       </c>
       <c r="J44">
-        <v>0.308</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2699,31 +2705,31 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C45">
-        <v>127</v>
+        <v>6</v>
       </c>
       <c r="D45">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E45">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G45">
-        <v>118</v>
+        <v>6</v>
       </c>
       <c r="H45">
-        <v>0.071</v>
+        <v>0</v>
       </c>
       <c r="I45">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="J45">
-        <v>0.122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2731,159 +2737,159 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C46">
-        <v>164</v>
+        <v>12</v>
       </c>
       <c r="D46">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G46">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47">
+        <v>20</v>
+      </c>
+      <c r="D47">
+        <v>26</v>
+      </c>
+      <c r="E47">
         <v>14</v>
       </c>
-      <c r="C47">
-        <v>180</v>
-      </c>
-      <c r="D47">
-        <v>20</v>
-      </c>
-      <c r="E47">
-        <v>18</v>
-      </c>
       <c r="F47">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G47">
-        <v>162</v>
+        <v>6</v>
       </c>
       <c r="H47">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="I47">
-        <v>0.9</v>
+        <v>0.538</v>
       </c>
       <c r="J47">
-        <v>0.18</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C48">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D48">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E48">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F48">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G48">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H48">
-        <v>0.302</v>
+        <v>0.32</v>
       </c>
       <c r="I48">
-        <v>0.65</v>
+        <v>0.308</v>
       </c>
       <c r="J48">
-        <v>0.413</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D49">
+        <v>26</v>
+      </c>
+      <c r="E49">
         <v>20</v>
       </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
       <c r="F49">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G49">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C50">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="D50">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F50">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G50">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2891,31 +2897,31 @@
         <v>24</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C51">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D51">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E51">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G51">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H51">
-        <v>0.707</v>
+        <v>0.438</v>
       </c>
       <c r="I51">
-        <v>0.879</v>
+        <v>0.538</v>
       </c>
       <c r="J51">
-        <v>0.784</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -2923,31 +2929,31 @@
         <v>24</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C52">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="D52">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E52">
         <v>2</v>
       </c>
       <c r="F52">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G52">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="H52">
-        <v>0.029</v>
+        <v>0.286</v>
       </c>
       <c r="I52">
-        <v>0.061</v>
+        <v>0.077</v>
       </c>
       <c r="J52">
-        <v>0.039</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2955,31 +2961,31 @@
         <v>24</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C53">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="D53">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E53">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F53">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G53">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="H53">
-        <v>0.225</v>
+        <v>0.455</v>
       </c>
       <c r="I53">
-        <v>0.606</v>
+        <v>0.192</v>
       </c>
       <c r="J53">
-        <v>0.328</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2987,31 +2993,31 @@
         <v>24</v>
       </c>
       <c r="B54" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C54">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="D54">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E54">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F54">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G54">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="H54">
-        <v>0.167</v>
+        <v>0.238</v>
       </c>
       <c r="I54">
-        <v>0.394</v>
+        <v>0.192</v>
       </c>
       <c r="J54">
-        <v>0.234</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -3019,95 +3025,95 @@
         <v>24</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C55">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="D55">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E55">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G55">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H55">
-        <v>0.821</v>
+        <v>0</v>
       </c>
       <c r="I55">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="J55">
-        <v>0.889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="D56">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F56">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>0.207</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C57">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="D57">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F57">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G57">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>0.071</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -3115,31 +3121,31 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C58">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="D58">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E58">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G58">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="H58">
-        <v>0.379</v>
+        <v>0</v>
       </c>
       <c r="I58">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="J58">
-        <v>0.407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -3147,31 +3153,31 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C59">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="D59">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F59">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G59">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="H59">
-        <v>0.073</v>
+        <v>0.1</v>
       </c>
       <c r="I59">
-        <v>0.16</v>
+        <v>0.9</v>
       </c>
       <c r="J59">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -3179,31 +3185,31 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60">
+        <v>43</v>
+      </c>
+      <c r="D60">
+        <v>20</v>
+      </c>
+      <c r="E60">
         <v>13</v>
       </c>
-      <c r="C60">
-        <v>40</v>
-      </c>
-      <c r="D60">
-        <v>25</v>
-      </c>
-      <c r="E60">
-        <v>14</v>
-      </c>
       <c r="F60">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G60">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H60">
-        <v>0.35</v>
+        <v>0.302</v>
       </c>
       <c r="I60">
-        <v>0.56</v>
+        <v>0.65</v>
       </c>
       <c r="J60">
-        <v>0.431</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -3211,31 +3217,31 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C61">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D61">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E61">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F61">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G61">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="H61">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="I61">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="J61">
-        <v>0.261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -3243,31 +3249,31 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C62">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D62">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E62">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F62">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G62">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H62">
-        <v>0.429</v>
+        <v>0.273</v>
       </c>
       <c r="I62">
-        <v>0.48</v>
+        <v>0.15</v>
       </c>
       <c r="J62">
-        <v>0.453</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -3275,31 +3281,31 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="D63">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="H63">
-        <v>0.25</v>
+        <v>0.043</v>
       </c>
       <c r="I63">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="J63">
-        <v>0.069</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -3307,22 +3313,22 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C64">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D64">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E64">
         <v>0</v>
       </c>
       <c r="F64">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G64">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -3342,28 +3348,28 @@
         <v>11</v>
       </c>
       <c r="C65">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D65">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E65">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G65">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H65">
-        <v>0.65</v>
+        <v>0.707</v>
       </c>
       <c r="I65">
-        <v>0.684</v>
+        <v>0.879</v>
       </c>
       <c r="J65">
-        <v>0.667</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -3374,28 +3380,28 @@
         <v>12</v>
       </c>
       <c r="C66">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="D66">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E66">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F66">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G66">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="H66">
-        <v>0.346</v>
+        <v>0.029</v>
       </c>
       <c r="I66">
-        <v>0.474</v>
+        <v>0.061</v>
       </c>
       <c r="J66">
-        <v>0.4</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -3406,28 +3412,28 @@
         <v>13</v>
       </c>
       <c r="C67">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="D67">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E67">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F67">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="H67">
-        <v>0.778</v>
+        <v>0.225</v>
       </c>
       <c r="I67">
-        <v>0.737</v>
+        <v>0.606</v>
       </c>
       <c r="J67">
-        <v>0.757</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -3438,28 +3444,28 @@
         <v>14</v>
       </c>
       <c r="C68">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="D68">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E68">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F68">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G68">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="H68">
-        <v>0.222</v>
+        <v>0.167</v>
       </c>
       <c r="I68">
-        <v>0.316</v>
+        <v>0.394</v>
       </c>
       <c r="J68">
-        <v>0.261</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -3470,28 +3476,28 @@
         <v>15</v>
       </c>
       <c r="C69">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D69">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E69">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F69">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H69">
-        <v>0.733</v>
+        <v>0.821</v>
       </c>
       <c r="I69">
-        <v>0.579</v>
+        <v>0.97</v>
       </c>
       <c r="J69">
-        <v>0.647</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -3502,28 +3508,28 @@
         <v>16</v>
       </c>
       <c r="C70">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D70">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E70">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F70">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G70">
         <v>2</v>
       </c>
       <c r="H70">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="I70">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="J70">
-        <v>0.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3534,92 +3540,92 @@
         <v>17</v>
       </c>
       <c r="C71">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D71">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E71">
+        <v>8</v>
+      </c>
+      <c r="F71">
+        <v>25</v>
+      </c>
+      <c r="G71">
         <v>2</v>
       </c>
-      <c r="F71">
-        <v>17</v>
-      </c>
-      <c r="G71">
-        <v>3</v>
-      </c>
       <c r="H71">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I71">
-        <v>0.105</v>
+        <v>0.242</v>
       </c>
       <c r="J71">
-        <v>0.167</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B72" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C72">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D72">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E72">
         <v>5</v>
       </c>
       <c r="F72">
+        <v>28</v>
+      </c>
+      <c r="G72">
         <v>19</v>
       </c>
-      <c r="G72">
-        <v>18</v>
-      </c>
       <c r="H72">
-        <v>0.217</v>
+        <v>0.208</v>
       </c>
       <c r="I72">
-        <v>0.208</v>
+        <v>0.152</v>
       </c>
       <c r="J72">
-        <v>0.213</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C73">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D73">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F73">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G73">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="H73">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="I73">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="J73">
-        <v>0.078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3627,31 +3633,31 @@
         <v>27</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C74">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D74">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F74">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G74">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H74">
-        <v>0.087</v>
+        <v>0.379</v>
       </c>
       <c r="I74">
-        <v>0.167</v>
+        <v>0.44</v>
       </c>
       <c r="J74">
-        <v>0.114</v>
+        <v>0.407</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3659,31 +3665,31 @@
         <v>27</v>
       </c>
       <c r="B75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C75">
+        <v>55</v>
+      </c>
+      <c r="D75">
+        <v>25</v>
+      </c>
+      <c r="E75">
+        <v>4</v>
+      </c>
+      <c r="F75">
+        <v>21</v>
+      </c>
+      <c r="G75">
         <v>51</v>
       </c>
-      <c r="D75">
-        <v>24</v>
-      </c>
-      <c r="E75">
-        <v>6</v>
-      </c>
-      <c r="F75">
-        <v>18</v>
-      </c>
-      <c r="G75">
-        <v>45</v>
-      </c>
       <c r="H75">
-        <v>0.118</v>
+        <v>0.073</v>
       </c>
       <c r="I75">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="J75">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3691,31 +3697,31 @@
         <v>27</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C76">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="D76">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E76">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F76">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G76">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="H76">
-        <v>0.091</v>
+        <v>0.35</v>
       </c>
       <c r="I76">
-        <v>0.292</v>
+        <v>0.56</v>
       </c>
       <c r="J76">
-        <v>0.139</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3723,31 +3729,31 @@
         <v>27</v>
       </c>
       <c r="B77" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77">
+        <v>44</v>
+      </c>
+      <c r="D77">
+        <v>25</v>
+      </c>
+      <c r="E77">
+        <v>9</v>
+      </c>
+      <c r="F77">
         <v>16</v>
       </c>
-      <c r="C77">
-        <v>7</v>
-      </c>
-      <c r="D77">
-        <v>24</v>
-      </c>
-      <c r="E77">
-        <v>3</v>
-      </c>
-      <c r="F77">
-        <v>21</v>
-      </c>
       <c r="G77">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="H77">
-        <v>0.429</v>
+        <v>0.205</v>
       </c>
       <c r="I77">
-        <v>0.125</v>
+        <v>0.36</v>
       </c>
       <c r="J77">
-        <v>0.194</v>
+        <v>0.261</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3755,159 +3761,159 @@
         <v>27</v>
       </c>
       <c r="B78" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C78">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D78">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F78">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G78">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H78">
-        <v>0.091</v>
+        <v>0.429</v>
       </c>
       <c r="I78">
-        <v>0.125</v>
+        <v>0.48</v>
       </c>
       <c r="J78">
-        <v>0.105</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B79" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C79">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="D79">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G79">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="H79">
-        <v>0.014</v>
+        <v>0.25</v>
       </c>
       <c r="I79">
-        <v>0.062</v>
+        <v>0.04</v>
       </c>
       <c r="J79">
-        <v>0.022</v>
+        <v>0.069</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C80">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="D80">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F80">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G80">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H80">
-        <v>0.044</v>
+        <v>0.333</v>
       </c>
       <c r="I80">
-        <v>0.188</v>
+        <v>0.2</v>
       </c>
       <c r="J80">
-        <v>0.071</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C81">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D81">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E81">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F81">
+        <v>21</v>
+      </c>
+      <c r="G81">
         <v>14</v>
       </c>
-      <c r="G81">
-        <v>73</v>
-      </c>
       <c r="H81">
-        <v>0.027</v>
+        <v>0.222</v>
       </c>
       <c r="I81">
-        <v>0.125</v>
+        <v>0.16</v>
       </c>
       <c r="J81">
-        <v>0.044</v>
+        <v>0.186</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C82">
-        <v>116</v>
+        <v>9</v>
       </c>
       <c r="D82">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F82">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G82">
-        <v>114</v>
+        <v>9</v>
       </c>
       <c r="H82">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="I82">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="J82">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -3915,31 +3921,31 @@
         <v>28</v>
       </c>
       <c r="B83" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C83">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D83">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F83">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G83">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H83">
-        <v>0.04</v>
+        <v>0.65</v>
       </c>
       <c r="I83">
-        <v>0.062</v>
+        <v>0.684</v>
       </c>
       <c r="J83">
-        <v>0.049</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -3947,31 +3953,31 @@
         <v>28</v>
       </c>
       <c r="B84" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C84">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D84">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F84">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G84">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="I84">
-        <v>0</v>
+        <v>0.474</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -3979,223 +3985,223 @@
         <v>28</v>
       </c>
       <c r="B85" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C85">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D85">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F85">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G85">
         <v>4</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>0.778</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>0.737</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>0.757</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B86" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C86">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D86">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F86">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G86">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="I86">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>0.261</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B87" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C87">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="D87">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F87">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="G87">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B88" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C88">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D88">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F88">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G88">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="I88">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B89" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C89">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D89">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G89">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H89">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="I89">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="J89">
-        <v>0.037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C90">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D90">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G90">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H90">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="I90">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="J90">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B91" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C91">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D91">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F91">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G91">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I91">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="J91">
-        <v>0</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -4203,254 +4209,1150 @@
         <v>29</v>
       </c>
       <c r="B92" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C92">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D92">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F92">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G92">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="H92">
-        <v>0</v>
+        <v>0.217</v>
       </c>
       <c r="I92">
-        <v>0</v>
+        <v>0.208</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B93" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C93">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="D93">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E93">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F93">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G93">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H93">
-        <v>0.6</v>
+        <v>0.057</v>
       </c>
       <c r="I93">
-        <v>0.45</v>
+        <v>0.125</v>
       </c>
       <c r="J93">
-        <v>0.514</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B94" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C94">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="D94">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E94">
         <v>4</v>
       </c>
       <c r="F94">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G94">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="H94">
-        <v>0.4</v>
+        <v>0.087</v>
       </c>
       <c r="I94">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="J94">
-        <v>0.267</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C95">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D95">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E95">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F95">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G95">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="H95">
-        <v>0.6</v>
+        <v>0.118</v>
       </c>
       <c r="I95">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="J95">
-        <v>0.6</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B96" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C96">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D96">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E96">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F96">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G96">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="H96">
-        <v>0.022</v>
+        <v>0.091</v>
       </c>
       <c r="I96">
-        <v>0.05</v>
+        <v>0.292</v>
       </c>
       <c r="J96">
-        <v>0.031</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B97" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C97">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D97">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E97">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F97">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H97">
-        <v>0.583</v>
+        <v>0.429</v>
       </c>
       <c r="I97">
-        <v>0.35</v>
+        <v>0.125</v>
       </c>
       <c r="J97">
-        <v>0.438</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B98" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C98">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D98">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F98">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G98">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H98">
-        <v>0.333</v>
+        <v>0.071</v>
       </c>
       <c r="I98">
-        <v>0.15</v>
+        <v>0.042</v>
       </c>
       <c r="J98">
-        <v>0.207</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" t="s">
+        <v>29</v>
+      </c>
+      <c r="B99" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99">
+        <v>42</v>
+      </c>
+      <c r="D99">
+        <v>24</v>
+      </c>
+      <c r="E99">
+        <v>5</v>
+      </c>
+      <c r="F99">
+        <v>19</v>
+      </c>
+      <c r="G99">
+        <v>37</v>
+      </c>
+      <c r="H99">
+        <v>0.119</v>
+      </c>
+      <c r="I99">
+        <v>0.208</v>
+      </c>
+      <c r="J99">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" t="s">
+        <v>29</v>
+      </c>
+      <c r="B100" t="s">
+        <v>19</v>
+      </c>
+      <c r="C100">
+        <v>33</v>
+      </c>
+      <c r="D100">
+        <v>24</v>
+      </c>
+      <c r="E100">
+        <v>3</v>
+      </c>
+      <c r="F100">
+        <v>21</v>
+      </c>
+      <c r="G100">
         <v>30</v>
       </c>
-      <c r="B99" t="s">
+      <c r="H100">
+        <v>0.091</v>
+      </c>
+      <c r="I100">
+        <v>0.125</v>
+      </c>
+      <c r="J100">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" t="s">
+        <v>30</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101">
+        <v>73</v>
+      </c>
+      <c r="D101">
+        <v>16</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101">
+        <v>15</v>
+      </c>
+      <c r="G101">
+        <v>72</v>
+      </c>
+      <c r="H101">
+        <v>0.014</v>
+      </c>
+      <c r="I101">
+        <v>0.062</v>
+      </c>
+      <c r="J101">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" t="s">
+        <v>30</v>
+      </c>
+      <c r="B102" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102">
+        <v>68</v>
+      </c>
+      <c r="D102">
+        <v>16</v>
+      </c>
+      <c r="E102">
+        <v>3</v>
+      </c>
+      <c r="F102">
+        <v>13</v>
+      </c>
+      <c r="G102">
+        <v>65</v>
+      </c>
+      <c r="H102">
+        <v>0.044</v>
+      </c>
+      <c r="I102">
+        <v>0.188</v>
+      </c>
+      <c r="J102">
+        <v>0.071</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" t="s">
+        <v>30</v>
+      </c>
+      <c r="B103" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103">
+        <v>75</v>
+      </c>
+      <c r="D103">
+        <v>16</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+      <c r="F103">
+        <v>14</v>
+      </c>
+      <c r="G103">
+        <v>73</v>
+      </c>
+      <c r="H103">
+        <v>0.027</v>
+      </c>
+      <c r="I103">
+        <v>0.125</v>
+      </c>
+      <c r="J103">
+        <v>0.044</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" t="s">
+        <v>30</v>
+      </c>
+      <c r="B104" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104">
+        <v>116</v>
+      </c>
+      <c r="D104">
+        <v>16</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
+      </c>
+      <c r="F104">
+        <v>14</v>
+      </c>
+      <c r="G104">
+        <v>114</v>
+      </c>
+      <c r="H104">
+        <v>0.017</v>
+      </c>
+      <c r="I104">
+        <v>0.125</v>
+      </c>
+      <c r="J104">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" t="s">
+        <v>30</v>
+      </c>
+      <c r="B105" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105">
+        <v>25</v>
+      </c>
+      <c r="D105">
+        <v>16</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="F105">
+        <v>15</v>
+      </c>
+      <c r="G105">
+        <v>24</v>
+      </c>
+      <c r="H105">
+        <v>0.04</v>
+      </c>
+      <c r="I105">
+        <v>0.062</v>
+      </c>
+      <c r="J105">
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" t="s">
+        <v>30</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106">
+        <v>3</v>
+      </c>
+      <c r="D106">
+        <v>16</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>16</v>
+      </c>
+      <c r="G106">
+        <v>3</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" t="s">
+        <v>30</v>
+      </c>
+      <c r="B107" t="s">
         <v>17</v>
       </c>
-      <c r="C99">
+      <c r="C107">
+        <v>6</v>
+      </c>
+      <c r="D107">
+        <v>16</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>16</v>
+      </c>
+      <c r="G107">
+        <v>6</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" t="s">
+        <v>30</v>
+      </c>
+      <c r="B108" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108">
+        <v>14</v>
+      </c>
+      <c r="D108">
+        <v>16</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>16</v>
+      </c>
+      <c r="G108">
+        <v>14</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" t="s">
+        <v>30</v>
+      </c>
+      <c r="B109" t="s">
+        <v>19</v>
+      </c>
+      <c r="C109">
+        <v>4</v>
+      </c>
+      <c r="D109">
+        <v>16</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>16</v>
+      </c>
+      <c r="G109">
+        <v>4</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" t="s">
+        <v>31</v>
+      </c>
+      <c r="B110" t="s">
         <v>11</v>
       </c>
-      <c r="D99">
+      <c r="C110">
+        <v>45</v>
+      </c>
+      <c r="D110">
+        <v>22</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>22</v>
+      </c>
+      <c r="G110">
+        <v>45</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" t="s">
+        <v>31</v>
+      </c>
+      <c r="B111" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111">
+        <v>52</v>
+      </c>
+      <c r="D111">
+        <v>22</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>22</v>
+      </c>
+      <c r="G111">
+        <v>52</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" t="s">
+        <v>31</v>
+      </c>
+      <c r="B112" t="s">
+        <v>13</v>
+      </c>
+      <c r="C112">
+        <v>40</v>
+      </c>
+      <c r="D112">
+        <v>22</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>22</v>
+      </c>
+      <c r="G112">
+        <v>40</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" t="s">
+        <v>31</v>
+      </c>
+      <c r="B113" t="s">
+        <v>14</v>
+      </c>
+      <c r="C113">
+        <v>32</v>
+      </c>
+      <c r="D113">
+        <v>22</v>
+      </c>
+      <c r="E113">
+        <v>1</v>
+      </c>
+      <c r="F113">
+        <v>21</v>
+      </c>
+      <c r="G113">
+        <v>31</v>
+      </c>
+      <c r="H113">
+        <v>0.031</v>
+      </c>
+      <c r="I113">
+        <v>0.045</v>
+      </c>
+      <c r="J113">
+        <v>0.037</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" t="s">
+        <v>31</v>
+      </c>
+      <c r="B114" t="s">
+        <v>15</v>
+      </c>
+      <c r="C114">
+        <v>18</v>
+      </c>
+      <c r="D114">
+        <v>22</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+      <c r="F114">
+        <v>21</v>
+      </c>
+      <c r="G114">
+        <v>17</v>
+      </c>
+      <c r="H114">
+        <v>0.056</v>
+      </c>
+      <c r="I114">
+        <v>0.045</v>
+      </c>
+      <c r="J114">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" t="s">
+        <v>31</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115">
+        <v>11</v>
+      </c>
+      <c r="D115">
+        <v>22</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>22</v>
+      </c>
+      <c r="G115">
+        <v>11</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" t="s">
+        <v>31</v>
+      </c>
+      <c r="B116" t="s">
+        <v>17</v>
+      </c>
+      <c r="C116">
+        <v>7</v>
+      </c>
+      <c r="D116">
+        <v>22</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>22</v>
+      </c>
+      <c r="G116">
+        <v>7</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" t="s">
+        <v>31</v>
+      </c>
+      <c r="B117" t="s">
+        <v>18</v>
+      </c>
+      <c r="C117">
+        <v>6</v>
+      </c>
+      <c r="D117">
+        <v>22</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>22</v>
+      </c>
+      <c r="G117">
+        <v>6</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" t="s">
+        <v>31</v>
+      </c>
+      <c r="B118" t="s">
+        <v>19</v>
+      </c>
+      <c r="C118">
+        <v>35</v>
+      </c>
+      <c r="D118">
+        <v>22</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>22</v>
+      </c>
+      <c r="G118">
+        <v>35</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" t="s">
+        <v>32</v>
+      </c>
+      <c r="B119" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119">
+        <v>15</v>
+      </c>
+      <c r="D119">
         <v>20</v>
       </c>
-      <c r="E99">
+      <c r="E119">
+        <v>9</v>
+      </c>
+      <c r="F119">
+        <v>11</v>
+      </c>
+      <c r="G119">
+        <v>6</v>
+      </c>
+      <c r="H119">
+        <v>0.6</v>
+      </c>
+      <c r="I119">
+        <v>0.45</v>
+      </c>
+      <c r="J119">
+        <v>0.514</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120" t="s">
+        <v>32</v>
+      </c>
+      <c r="B120" t="s">
+        <v>12</v>
+      </c>
+      <c r="C120">
+        <v>10</v>
+      </c>
+      <c r="D120">
+        <v>20</v>
+      </c>
+      <c r="E120">
+        <v>4</v>
+      </c>
+      <c r="F120">
+        <v>16</v>
+      </c>
+      <c r="G120">
+        <v>6</v>
+      </c>
+      <c r="H120">
+        <v>0.4</v>
+      </c>
+      <c r="I120">
+        <v>0.2</v>
+      </c>
+      <c r="J120">
+        <v>0.267</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="A121" t="s">
+        <v>32</v>
+      </c>
+      <c r="B121" t="s">
+        <v>13</v>
+      </c>
+      <c r="C121">
+        <v>20</v>
+      </c>
+      <c r="D121">
+        <v>20</v>
+      </c>
+      <c r="E121">
+        <v>12</v>
+      </c>
+      <c r="F121">
+        <v>8</v>
+      </c>
+      <c r="G121">
+        <v>8</v>
+      </c>
+      <c r="H121">
+        <v>0.6</v>
+      </c>
+      <c r="I121">
+        <v>0.6</v>
+      </c>
+      <c r="J121">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="A122" t="s">
+        <v>32</v>
+      </c>
+      <c r="B122" t="s">
+        <v>14</v>
+      </c>
+      <c r="C122">
+        <v>45</v>
+      </c>
+      <c r="D122">
+        <v>20</v>
+      </c>
+      <c r="E122">
+        <v>1</v>
+      </c>
+      <c r="F122">
+        <v>19</v>
+      </c>
+      <c r="G122">
+        <v>44</v>
+      </c>
+      <c r="H122">
+        <v>0.022</v>
+      </c>
+      <c r="I122">
+        <v>0.05</v>
+      </c>
+      <c r="J122">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123" t="s">
+        <v>32</v>
+      </c>
+      <c r="B123" t="s">
+        <v>15</v>
+      </c>
+      <c r="C123">
+        <v>12</v>
+      </c>
+      <c r="D123">
+        <v>20</v>
+      </c>
+      <c r="E123">
+        <v>7</v>
+      </c>
+      <c r="F123">
+        <v>13</v>
+      </c>
+      <c r="G123">
+        <v>5</v>
+      </c>
+      <c r="H123">
+        <v>0.583</v>
+      </c>
+      <c r="I123">
+        <v>0.35</v>
+      </c>
+      <c r="J123">
+        <v>0.438</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124" t="s">
+        <v>32</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124">
+        <v>9</v>
+      </c>
+      <c r="D124">
+        <v>20</v>
+      </c>
+      <c r="E124">
+        <v>3</v>
+      </c>
+      <c r="F124">
+        <v>17</v>
+      </c>
+      <c r="G124">
+        <v>6</v>
+      </c>
+      <c r="H124">
+        <v>0.333</v>
+      </c>
+      <c r="I124">
+        <v>0.15</v>
+      </c>
+      <c r="J124">
+        <v>0.207</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125" t="s">
+        <v>32</v>
+      </c>
+      <c r="B125" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125">
+        <v>9</v>
+      </c>
+      <c r="D125">
+        <v>20</v>
+      </c>
+      <c r="E125">
+        <v>4</v>
+      </c>
+      <c r="F125">
+        <v>16</v>
+      </c>
+      <c r="G125">
+        <v>5</v>
+      </c>
+      <c r="H125">
+        <v>0.444</v>
+      </c>
+      <c r="I125">
+        <v>0.2</v>
+      </c>
+      <c r="J125">
+        <v>0.276</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126" t="s">
+        <v>32</v>
+      </c>
+      <c r="B126" t="s">
+        <v>18</v>
+      </c>
+      <c r="C126">
+        <v>14</v>
+      </c>
+      <c r="D126">
+        <v>20</v>
+      </c>
+      <c r="E126">
+        <v>3</v>
+      </c>
+      <c r="F126">
+        <v>17</v>
+      </c>
+      <c r="G126">
+        <v>11</v>
+      </c>
+      <c r="H126">
+        <v>0.214</v>
+      </c>
+      <c r="I126">
+        <v>0.15</v>
+      </c>
+      <c r="J126">
+        <v>0.176</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="A127" t="s">
+        <v>32</v>
+      </c>
+      <c r="B127" t="s">
+        <v>19</v>
+      </c>
+      <c r="C127">
+        <v>11</v>
+      </c>
+      <c r="D127">
+        <v>20</v>
+      </c>
+      <c r="E127">
         <v>2</v>
       </c>
-      <c r="F99">
+      <c r="F127">
         <v>18</v>
       </c>
-      <c r="G99">
+      <c r="G127">
         <v>9</v>
       </c>
-      <c r="H99">
+      <c r="H127">
         <v>0.182</v>
       </c>
-      <c r="I99">
+      <c r="I127">
         <v>0.1</v>
       </c>
-      <c r="J99">
+      <c r="J127">
         <v>0.129</v>
       </c>
     </row>
